--- a/docs/Files/Mid-format_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
+++ b/docs/Files/Mid-format_model/ODYM_T6_RecyclingToOtherProduction_V1.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852776F-CA67-4130-98EC-078E191CDB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E195D85-21F1-429E-A857-67D1E7424825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -318,12 +318,6 @@
     <t>LIB materials</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
     <t>Preprocessing and recycling</t>
   </si>
   <si>
@@ -343,6 +337,12 @@
   </si>
   <si>
     <t>ODYM_Classifications_MF</t>
+  </si>
+  <si>
+    <t>MF LIB</t>
+  </si>
+  <si>
+    <t>other MF LIB products</t>
   </si>
 </sst>
 </file>
@@ -799,7 +799,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -813,7 +813,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -869,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -883,7 +883,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -897,7 +897,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -967,7 +967,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1189,7 +1189,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1215,7 +1215,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>0.7</v>
@@ -1230,7 +1230,7 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1241,7 +1241,7 @@
         <v>94</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1267,7 +1267,7 @@
         <v>94</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>0.7</v>
@@ -1282,7 +1282,7 @@
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.35">
